--- a/data/kfmp_transect_video_species_260103.xlsx
+++ b/data/kfmp_transect_video_species_260103.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elahi/Desktop/video_qual_sheets_2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elahi/Desktop/video_qual_sheets_2025/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98112E8-9892-6641-81EC-3B97C73A8C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59590EBE-F7A4-744F-B168-F136715DAB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="25700" windowHeight="15680" xr2:uid="{047547D0-BD10-354A-81F3-2D277E17EFCC}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18420" xr2:uid="{047547D0-BD10-354A-81F3-2D277E17EFCC}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="179">
   <si>
     <t>Polymastia_pachymastia</t>
   </si>
@@ -565,6 +565,18 @@
   <si>
     <t>view</t>
   </si>
+  <si>
+    <t>site</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>bird_rock</t>
+  </si>
+  <si>
+    <t>hms100</t>
+  </si>
 </sst>
 </file>
 
@@ -793,7 +805,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment textRotation="90"/>
@@ -828,10 +840,9 @@
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
@@ -1203,438 +1214,446 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68E13376-6688-6B43-97F6-8BA76DA6F166}">
-  <dimension ref="A1:DY13"/>
+  <dimension ref="A1:EA13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5" customWidth="1"/>
-    <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="129" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5" customWidth="1"/>
+    <col min="5" max="5" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="131" width="3.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:129" s="43" customFormat="1" ht="178" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:131" s="42" customFormat="1" ht="178" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="E1" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="F1" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="G1" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="H1" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="I1" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="J1" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="K1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="L1" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="K1" s="35" t="s">
+      <c r="M1" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="36" t="s">
+      <c r="N1" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="M1" s="36" t="s">
+      <c r="O1" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="N1" s="37" t="s">
+      <c r="P1" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="O1" s="33" t="s">
+      <c r="Q1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="38" t="s">
+      <c r="R1" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="R1" s="39" t="s">
+      <c r="T1" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="S1" s="39" t="s">
+      <c r="U1" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="T1" s="40" t="s">
+      <c r="V1" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="39" t="s">
+      <c r="W1" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="V1" s="39" t="s">
+      <c r="X1" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="W1" s="39" t="s">
+      <c r="Y1" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="X1" s="41" t="s">
+      <c r="Z1" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" s="41" t="s">
+      <c r="AA1" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="Z1" s="35" t="s">
+      <c r="AB1" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="AA1" s="35" t="s">
+      <c r="AC1" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="AB1" s="39" t="s">
+      <c r="AD1" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="AC1" s="40" t="s">
+      <c r="AE1" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="AD1" s="34" t="s">
+      <c r="AF1" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="AE1" s="34" t="s">
+      <c r="AG1" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="AF1" s="33" t="s">
+      <c r="AH1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="AG1" s="35" t="s">
+      <c r="AI1" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="33" t="s">
+      <c r="AJ1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="AI1" s="35" t="s">
+      <c r="AK1" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="AJ1" s="39" t="s">
+      <c r="AL1" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="AK1" s="36" t="s">
+      <c r="AM1" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="AL1" s="36" t="s">
+      <c r="AN1" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="AM1" s="35" t="s">
+      <c r="AO1" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="AN1" s="36" t="s">
+      <c r="AP1" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="AO1" s="32" t="s">
+      <c r="AQ1" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="AP1" s="41" t="s">
+      <c r="AR1" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="32" t="s">
+      <c r="AS1" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="AR1" s="34" t="s">
+      <c r="AT1" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="AS1" s="34" t="s">
+      <c r="AU1" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="AT1" s="37" t="s">
+      <c r="AV1" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="AU1" s="37" t="s">
+      <c r="AW1" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="AV1" s="37" t="s">
+      <c r="AX1" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="AW1" s="35" t="s">
+      <c r="AY1" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="AX1" s="32" t="s">
+      <c r="AZ1" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="AY1" s="40" t="s">
+      <c r="BA1" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="AZ1" s="40" t="s">
+      <c r="BB1" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="BA1" s="37" t="s">
+      <c r="BC1" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="BB1" s="39" t="s">
+      <c r="BD1" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="BC1" s="39" t="s">
+      <c r="BE1" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="BD1" s="40" t="s">
+      <c r="BF1" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="BE1" s="39" t="s">
+      <c r="BG1" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="BF1" s="36" t="s">
+      <c r="BH1" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="BG1" s="40" t="s">
+      <c r="BI1" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="BH1" s="41" t="s">
+      <c r="BJ1" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="BI1" s="40" t="s">
+      <c r="BK1" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="BJ1" s="35" t="s">
+      <c r="BL1" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="BK1" s="41" t="s">
+      <c r="BM1" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="BL1" s="32" t="s">
+      <c r="BN1" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="BM1" s="38" t="s">
+      <c r="BO1" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="BN1" s="32" t="s">
+      <c r="BP1" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="BO1" s="40" t="s">
+      <c r="BQ1" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="BP1" s="35" t="s">
+      <c r="BR1" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="BQ1" s="36" t="s">
+      <c r="BS1" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="BR1" s="33" t="s">
+      <c r="BT1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="BS1" s="37" t="s">
+      <c r="BU1" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="BT1" s="35" t="s">
+      <c r="BV1" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="BU1" s="32" t="s">
+      <c r="BW1" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="BV1" s="40" t="s">
+      <c r="BX1" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="BW1" s="36" t="s">
+      <c r="BY1" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="BX1" s="40" t="s">
+      <c r="BZ1" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="BY1" s="40" t="s">
+      <c r="CA1" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="BZ1" s="33" t="s">
+      <c r="CB1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="CA1" s="33" t="s">
+      <c r="CC1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="CB1" s="40" t="s">
+      <c r="CD1" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="CC1" s="35" t="s">
+      <c r="CE1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="CD1" s="36" t="s">
+      <c r="CF1" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="CE1" s="40" t="s">
+      <c r="CG1" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="CF1" s="41" t="s">
+      <c r="CH1" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="CG1" s="40" t="s">
+      <c r="CI1" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="CH1" s="37" t="s">
+      <c r="CJ1" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="CI1" s="36" t="s">
+      <c r="CK1" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="CJ1" s="39" t="s">
+      <c r="CL1" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="CK1" s="34" t="s">
+      <c r="CM1" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="CL1" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="CM1" s="39" t="s">
+      <c r="CN1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="CO1" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="CN1" s="34" t="s">
+      <c r="CP1" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="CO1" s="36" t="s">
+      <c r="CQ1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="CP1" s="34" t="s">
+      <c r="CR1" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="CQ1" s="39" t="s">
+      <c r="CS1" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="CR1" s="39" t="s">
+      <c r="CT1" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="CS1" s="39" t="s">
+      <c r="CU1" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="CT1" s="41" t="s">
+      <c r="CV1" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="CU1" s="40" t="s">
+      <c r="CW1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="CV1" s="40" t="s">
+      <c r="CX1" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="CW1" s="40" t="s">
+      <c r="CY1" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="CX1" s="39" t="s">
+      <c r="CZ1" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="CY1" s="39" t="s">
+      <c r="DA1" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="CZ1" s="40" t="s">
+      <c r="DB1" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="DA1" s="40" t="s">
+      <c r="DC1" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="DB1" s="40" t="s">
+      <c r="DD1" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="DC1" s="40" t="s">
+      <c r="DE1" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="DD1" s="40" t="s">
+      <c r="DF1" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="DE1" s="40" t="s">
+      <c r="DG1" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="DF1" s="40" t="s">
+      <c r="DH1" s="39" t="s">
         <v>144</v>
       </c>
-      <c r="DG1" s="40" t="s">
+      <c r="DI1" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="DH1" s="40" t="s">
+      <c r="DJ1" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="DI1" s="40" t="s">
+      <c r="DK1" s="39" t="s">
         <v>141</v>
       </c>
-      <c r="DJ1" s="40" t="s">
+      <c r="DL1" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="DK1" s="40" t="s">
+      <c r="DM1" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="DL1" s="37" t="s">
+      <c r="DN1" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="DM1" s="32" t="s">
+      <c r="DO1" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="DN1" s="36" t="s">
+      <c r="DP1" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="DO1" s="34" t="s">
+      <c r="DQ1" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="DP1" s="33" t="s">
+      <c r="DR1" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="DQ1" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="DR1" s="34" t="s">
+      <c r="DS1" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="DT1" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="DS1" s="33" t="s">
+      <c r="DU1" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="DT1" s="33" t="s">
+      <c r="DV1" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="DU1" s="33" t="s">
+      <c r="DW1" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="DV1" s="33" t="s">
+      <c r="DX1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="DW1" s="33" t="s">
+      <c r="DY1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="DX1" s="33" t="s">
+      <c r="DZ1" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="DY1" s="41" t="s">
+      <c r="EA1" s="40" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:129" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
+    <row r="2" spans="1:131" x14ac:dyDescent="0.2">
+      <c r="A2" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="29" t="str">
+      <c r="B2" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="28">
+        <v>2023</v>
+      </c>
+      <c r="D2" s="28" t="str">
         <f>LEFT(A2,LEN(A2)-2)</f>
         <v>bird_rock_2023-08-30_t1</v>
       </c>
-      <c r="C2" s="29" t="str">
+      <c r="E2" s="28" t="str">
         <f>RIGHT(A2, 1)</f>
         <v>k</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
         <v>129</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>129</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>2</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
       <c r="J2">
         <v>0</v>
       </c>
@@ -1654,13 +1673,13 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -1669,13 +1688,13 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2">
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2">
         <v>0</v>
@@ -1693,22 +1712,22 @@
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2">
         <v>0</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2">
         <v>0</v>
@@ -1741,13 +1760,13 @@
         <v>0</v>
       </c>
       <c r="AS2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT2">
         <v>0</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV2">
         <v>0</v>
@@ -1813,13 +1832,13 @@
         <v>0</v>
       </c>
       <c r="BQ2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR2">
         <v>0</v>
       </c>
       <c r="BS2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT2">
         <v>0</v>
@@ -1852,13 +1871,13 @@
         <v>0</v>
       </c>
       <c r="CD2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE2">
         <v>0</v>
       </c>
       <c r="CF2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG2">
         <v>0</v>
@@ -1867,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="CI2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ2">
         <v>0</v>
       </c>
       <c r="CK2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL2">
         <v>0</v>
@@ -1891,13 +1910,13 @@
         <v>0</v>
       </c>
       <c r="CQ2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR2">
         <v>0</v>
       </c>
       <c r="CS2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CT2">
         <v>0</v>
@@ -1951,31 +1970,31 @@
         <v>0</v>
       </c>
       <c r="DK2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DL2">
         <v>0</v>
       </c>
       <c r="DM2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DN2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO2">
         <v>0</v>
       </c>
       <c r="DP2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR2">
         <v>0</v>
       </c>
       <c r="DS2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT2">
         <v>0</v>
@@ -1995,37 +2014,43 @@
       <c r="DY2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:129" x14ac:dyDescent="0.2">
-      <c r="A3" s="29" t="s">
+      <c r="DZ2">
+        <v>0</v>
+      </c>
+      <c r="EA2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:131" x14ac:dyDescent="0.2">
+      <c r="A3" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="29" t="str">
-        <f t="shared" ref="B3:B13" si="0">LEFT(A3,LEN(A3)-2)</f>
+      <c r="B3" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C3" s="28">
+        <v>2023</v>
+      </c>
+      <c r="D3" s="28" t="str">
+        <f t="shared" ref="D3:D13" si="0">LEFT(A3,LEN(A3)-2)</f>
         <v>bird_rock_2023-08-30_t1</v>
       </c>
-      <c r="C3" s="29" t="str">
-        <f t="shared" ref="C3:C13" si="1">RIGHT(A3, 1)</f>
+      <c r="E3" s="28" t="str">
+        <f t="shared" ref="E3:E13" si="1">RIGHT(A3, 1)</f>
         <v>b</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
         <v>129</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>129</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
       <c r="J3">
         <v>0</v>
       </c>
@@ -2039,19 +2064,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>1</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -2060,22 +2085,22 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3">
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3">
         <v>0</v>
@@ -2093,13 +2118,13 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3">
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3">
         <v>0</v>
@@ -2108,13 +2133,13 @@
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN3">
         <v>0</v>
@@ -2129,43 +2154,43 @@
         <v>0</v>
       </c>
       <c r="AR3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV3">
         <v>0</v>
       </c>
       <c r="AW3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX3">
         <v>0</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ3">
         <v>0</v>
       </c>
       <c r="BA3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE3">
         <v>0</v>
@@ -2204,13 +2229,13 @@
         <v>0</v>
       </c>
       <c r="BQ3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR3">
         <v>0</v>
       </c>
       <c r="BS3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT3">
         <v>0</v>
@@ -2228,13 +2253,13 @@
         <v>0</v>
       </c>
       <c r="BY3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
         <v>0</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB3">
         <v>0</v>
@@ -2243,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="CD3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE3">
         <v>0</v>
       </c>
       <c r="CF3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG3">
         <v>0</v>
@@ -2282,13 +2307,13 @@
         <v>0</v>
       </c>
       <c r="CQ3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR3">
         <v>0</v>
       </c>
       <c r="CS3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CT3">
         <v>0</v>
@@ -2351,13 +2376,13 @@
         <v>0</v>
       </c>
       <c r="DN3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO3">
         <v>0</v>
       </c>
       <c r="DP3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ3">
         <v>0</v>
@@ -2386,37 +2411,43 @@
       <c r="DY3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:129" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
+      <c r="DZ3">
+        <v>0</v>
+      </c>
+      <c r="EA3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:131" x14ac:dyDescent="0.2">
+      <c r="A4" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="B4" s="29" t="str">
+      <c r="B4" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="28">
+        <v>2023</v>
+      </c>
+      <c r="D4" s="28" t="str">
         <f t="shared" si="0"/>
         <v>hms100_2023-08-30_t1</v>
       </c>
-      <c r="C4" s="29" t="str">
+      <c r="E4" s="28" t="str">
         <f t="shared" si="1"/>
         <v>k</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
         <v>129</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>129</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>2</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
       <c r="J4">
         <v>0</v>
       </c>
@@ -2451,22 +2482,22 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4">
         <v>0</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4">
         <v>0</v>
@@ -2478,13 +2509,13 @@
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4">
         <v>0</v>
@@ -2508,16 +2539,16 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2529,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV4">
         <v>0</v>
@@ -2574,25 +2605,25 @@
         <v>0</v>
       </c>
       <c r="BJ4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK4">
         <v>0</v>
       </c>
       <c r="BL4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM4">
         <v>0</v>
       </c>
       <c r="BN4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO4">
         <v>0</v>
       </c>
       <c r="BP4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ4">
         <v>0</v>
@@ -2634,22 +2665,22 @@
         <v>0</v>
       </c>
       <c r="CD4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE4">
         <v>0</v>
       </c>
       <c r="CF4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH4">
         <v>0</v>
       </c>
       <c r="CI4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ4">
         <v>0</v>
@@ -2739,13 +2770,13 @@
         <v>0</v>
       </c>
       <c r="DM4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN4">
         <v>0</v>
       </c>
       <c r="DO4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP4">
         <v>0</v>
@@ -2777,45 +2808,51 @@
       <c r="DY4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:129" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+      <c r="DZ4">
+        <v>0</v>
+      </c>
+      <c r="EA4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:131" x14ac:dyDescent="0.2">
+      <c r="A5" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="29" t="str">
+      <c r="B5" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="28">
+        <v>2023</v>
+      </c>
+      <c r="D5" s="28" t="str">
         <f t="shared" si="0"/>
         <v>hms100_2023-08-30_t1</v>
       </c>
-      <c r="C5" s="29" t="str">
+      <c r="E5" s="28" t="str">
         <f t="shared" si="1"/>
         <v>b</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
         <v>129</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>129</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>2</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -2824,13 +2861,13 @@
         <v>0</v>
       </c>
       <c r="O5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2839,25 +2876,25 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5">
         <v>1</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5">
         <v>0</v>
@@ -2875,13 +2912,13 @@
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5">
         <v>0</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5">
         <v>0</v>
@@ -2899,13 +2936,13 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ5">
         <v>1</v>
@@ -2914,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT5">
         <v>0</v>
@@ -2926,13 +2963,13 @@
         <v>0</v>
       </c>
       <c r="AW5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX5">
         <v>0</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ5">
         <v>0</v>
@@ -2965,13 +3002,13 @@
         <v>0</v>
       </c>
       <c r="BJ5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK5">
         <v>0</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM5">
         <v>0</v>
@@ -3025,13 +3062,13 @@
         <v>0</v>
       </c>
       <c r="CD5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE5">
         <v>0</v>
       </c>
       <c r="CF5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG5">
         <v>0</v>
@@ -3043,13 +3080,13 @@
         <v>0</v>
       </c>
       <c r="CJ5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK5">
         <v>0</v>
       </c>
       <c r="CL5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM5">
         <v>0</v>
@@ -3085,13 +3122,13 @@
         <v>0</v>
       </c>
       <c r="CX5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY5">
         <v>0</v>
       </c>
       <c r="CZ5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DA5">
         <v>0</v>
@@ -3130,16 +3167,16 @@
         <v>0</v>
       </c>
       <c r="DM5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ5">
         <v>0</v>
@@ -3168,45 +3205,51 @@
       <c r="DY5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:129" x14ac:dyDescent="0.2">
-      <c r="A6" s="30" t="s">
+      <c r="DZ5">
+        <v>0</v>
+      </c>
+      <c r="EA5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:131" x14ac:dyDescent="0.2">
+      <c r="A6" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="29" t="str">
+      <c r="B6" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="28">
+        <v>2024</v>
+      </c>
+      <c r="D6" s="28" t="str">
         <f t="shared" si="0"/>
         <v>bird_rock_2024-08-23_t1</v>
       </c>
-      <c r="C6" s="29" t="str">
+      <c r="E6" s="28" t="str">
         <f t="shared" si="1"/>
         <v>k</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>129</v>
-      </c>
-      <c r="F6" t="s">
-        <v>129</v>
+      <c r="F6">
+        <v>1</v>
       </c>
       <c r="G6" t="s">
         <v>129</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
+      <c r="H6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I6" t="s">
+        <v>129</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -3218,13 +3261,13 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -3233,13 +3276,13 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6">
         <v>0</v>
@@ -3266,13 +3309,13 @@
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6">
         <v>0</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6">
         <v>0</v>
@@ -3305,13 +3348,13 @@
         <v>0</v>
       </c>
       <c r="AS6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT6">
         <v>0</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV6">
         <v>0</v>
@@ -3329,13 +3372,13 @@
         <v>0</v>
       </c>
       <c r="BA6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB6">
         <v>0</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD6">
         <v>0</v>
@@ -3368,22 +3411,22 @@
         <v>0</v>
       </c>
       <c r="BN6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO6">
         <v>0</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR6">
         <v>0</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT6">
         <v>0</v>
@@ -3416,22 +3459,22 @@
         <v>0</v>
       </c>
       <c r="CD6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE6">
         <v>0</v>
       </c>
       <c r="CF6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH6">
         <v>0</v>
       </c>
       <c r="CI6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ6">
         <v>0</v>
@@ -3455,13 +3498,13 @@
         <v>0</v>
       </c>
       <c r="CQ6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR6">
         <v>0</v>
       </c>
       <c r="CS6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CT6">
         <v>0</v>
@@ -3506,16 +3549,16 @@
         <v>0</v>
       </c>
       <c r="DH6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DL6">
         <v>0</v>
@@ -3524,13 +3567,13 @@
         <v>0</v>
       </c>
       <c r="DN6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO6">
         <v>0</v>
       </c>
       <c r="DP6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ6">
         <v>0</v>
@@ -3548,59 +3591,65 @@
         <v>0</v>
       </c>
       <c r="DV6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW6">
         <v>0</v>
       </c>
       <c r="DX6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:129" x14ac:dyDescent="0.2">
-      <c r="A7" s="30" t="s">
+      <c r="DZ6">
+        <v>0</v>
+      </c>
+      <c r="EA6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:131" x14ac:dyDescent="0.2">
+      <c r="A7" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="B7" s="29" t="str">
+      <c r="B7" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="28">
+        <v>2024</v>
+      </c>
+      <c r="D7" s="28" t="str">
         <f t="shared" si="0"/>
         <v>bird_rock_2024-08-23_t1</v>
       </c>
-      <c r="C7" s="29" t="str">
+      <c r="E7" s="28" t="str">
         <f t="shared" si="1"/>
         <v>b</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>129</v>
-      </c>
-      <c r="F7" t="s">
-        <v>129</v>
+      <c r="F7">
+        <v>1</v>
       </c>
       <c r="G7" t="s">
         <v>129</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
+      <c r="H7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I7" t="s">
+        <v>129</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -3609,13 +3658,13 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -3624,16 +3673,16 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7">
         <v>0</v>
@@ -3651,43 +3700,43 @@
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7">
         <v>1</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7">
         <v>0</v>
       </c>
       <c r="AK7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7">
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
         <v>0</v>
@@ -3696,13 +3745,13 @@
         <v>0</v>
       </c>
       <c r="AS7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT7">
         <v>0</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV7">
         <v>0</v>
@@ -3720,16 +3769,16 @@
         <v>0</v>
       </c>
       <c r="BA7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE7">
         <v>0</v>
@@ -3768,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="BQ7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR7">
         <v>0</v>
@@ -3780,19 +3829,19 @@
         <v>0</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV7">
         <v>0</v>
       </c>
       <c r="BW7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BX7">
         <v>0</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -3807,13 +3856,13 @@
         <v>0</v>
       </c>
       <c r="CD7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE7">
         <v>0</v>
       </c>
       <c r="CF7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG7">
         <v>0</v>
@@ -3822,13 +3871,13 @@
         <v>0</v>
       </c>
       <c r="CI7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ7">
         <v>0</v>
       </c>
       <c r="CK7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL7">
         <v>0</v>
@@ -3846,16 +3895,16 @@
         <v>0</v>
       </c>
       <c r="CQ7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CS7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CT7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU7">
         <v>0</v>
@@ -3876,16 +3925,16 @@
         <v>0</v>
       </c>
       <c r="DA7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE7">
         <v>0</v>
@@ -3900,13 +3949,13 @@
         <v>0</v>
       </c>
       <c r="DI7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ7">
         <v>0</v>
       </c>
       <c r="DK7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DL7">
         <v>0</v>
@@ -3915,16 +3964,16 @@
         <v>0</v>
       </c>
       <c r="DN7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO7">
         <v>0</v>
       </c>
       <c r="DP7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR7">
         <v>0</v>
@@ -3936,59 +3985,65 @@
         <v>0</v>
       </c>
       <c r="DU7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW7">
         <v>0</v>
       </c>
       <c r="DX7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:129" x14ac:dyDescent="0.2">
-      <c r="A8" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="DZ7">
+        <v>0</v>
+      </c>
+      <c r="EA7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:131" x14ac:dyDescent="0.2">
+      <c r="A8" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="B8" s="29" t="str">
+      <c r="B8" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="28">
+        <v>2024</v>
+      </c>
+      <c r="D8" s="28" t="str">
         <f t="shared" si="0"/>
         <v>hms090_2024-08-23_t1</v>
       </c>
-      <c r="C8" s="29" t="str">
+      <c r="E8" s="28" t="str">
         <f t="shared" si="1"/>
         <v>k</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F8" t="s">
-        <v>129</v>
+      <c r="F8">
+        <v>1</v>
       </c>
       <c r="G8" t="s">
         <v>129</v>
       </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
+      <c r="H8" t="s">
+        <v>129</v>
+      </c>
+      <c r="I8" t="s">
+        <v>129</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -4015,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8">
         <v>0</v>
@@ -4081,13 +4136,13 @@
         <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR8">
         <v>0</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT8">
         <v>0</v>
@@ -4108,13 +4163,13 @@
         <v>0</v>
       </c>
       <c r="AZ8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA8">
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC8">
         <v>0</v>
@@ -4150,13 +4205,13 @@
         <v>0</v>
       </c>
       <c r="BN8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO8">
         <v>0</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ8">
         <v>0</v>
@@ -4207,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="CG8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH8">
         <v>0</v>
       </c>
       <c r="CI8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ8">
         <v>0</v>
@@ -4267,13 +4322,13 @@
         <v>0</v>
       </c>
       <c r="DA8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB8">
         <v>0</v>
       </c>
       <c r="DC8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD8">
         <v>0</v>
@@ -4282,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="DF8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG8">
         <v>0</v>
@@ -4291,25 +4346,25 @@
         <v>1</v>
       </c>
       <c r="DI8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DL8">
         <v>0</v>
       </c>
       <c r="DM8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN8">
         <v>0</v>
       </c>
       <c r="DO8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP8">
         <v>0</v>
@@ -4341,42 +4396,48 @@
       <c r="DY8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:129" x14ac:dyDescent="0.2">
-      <c r="A9" s="30" t="s">
+      <c r="DZ8">
+        <v>0</v>
+      </c>
+      <c r="EA8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:131" x14ac:dyDescent="0.2">
+      <c r="A9" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="B9" s="29" t="str">
+      <c r="B9" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" s="28">
+        <v>2024</v>
+      </c>
+      <c r="D9" s="28" t="str">
         <f t="shared" si="0"/>
         <v>hms090_2024-08-23_t1</v>
       </c>
-      <c r="C9" s="29" t="str">
+      <c r="E9" s="28" t="str">
         <f t="shared" si="1"/>
         <v>b</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>129</v>
-      </c>
-      <c r="F9" t="s">
-        <v>129</v>
+      <c r="F9">
+        <v>1</v>
       </c>
       <c r="G9" t="s">
         <v>129</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
+      <c r="H9" t="s">
+        <v>129</v>
+      </c>
+      <c r="I9" t="s">
+        <v>129</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -4388,22 +4449,22 @@
         <v>0</v>
       </c>
       <c r="O9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -4412,19 +4473,19 @@
         <v>0</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9">
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9">
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9">
         <v>0</v>
@@ -4433,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <v>0</v>
@@ -4445,7 +4506,7 @@
         <v>0</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9">
         <v>0</v>
@@ -4472,13 +4533,13 @@
         <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT9">
         <v>1</v>
@@ -4487,16 +4548,16 @@
         <v>0</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX9">
         <v>0</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ9">
         <v>0</v>
@@ -4541,13 +4602,13 @@
         <v>0</v>
       </c>
       <c r="BN9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO9">
         <v>0</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ9">
         <v>0</v>
@@ -4574,28 +4635,28 @@
         <v>0</v>
       </c>
       <c r="BY9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC9">
         <v>0</v>
       </c>
       <c r="CD9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE9">
         <v>0</v>
       </c>
       <c r="CF9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG9">
         <v>0</v>
@@ -4607,22 +4668,22 @@
         <v>0</v>
       </c>
       <c r="CJ9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK9">
         <v>0</v>
       </c>
       <c r="CL9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN9">
         <v>0</v>
       </c>
       <c r="CO9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP9">
         <v>0</v>
@@ -4649,25 +4710,25 @@
         <v>0</v>
       </c>
       <c r="CX9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY9">
         <v>0</v>
       </c>
       <c r="CZ9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DA9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB9">
         <v>0</v>
       </c>
       <c r="DC9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE9">
         <v>0</v>
@@ -4679,31 +4740,31 @@
         <v>0</v>
       </c>
       <c r="DH9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ9">
         <v>0</v>
       </c>
       <c r="DK9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DL9">
         <v>0</v>
       </c>
       <c r="DM9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ9">
         <v>0</v>
@@ -4732,45 +4793,51 @@
       <c r="DY9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:129" x14ac:dyDescent="0.2">
-      <c r="A10" s="30" t="s">
+      <c r="DZ9">
+        <v>0</v>
+      </c>
+      <c r="EA9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:131" x14ac:dyDescent="0.2">
+      <c r="A10" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="29" t="str">
+      <c r="B10" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" s="28">
+        <v>2025</v>
+      </c>
+      <c r="D10" s="28" t="str">
         <f t="shared" si="0"/>
         <v>bird_rock_2025-09-11_t1</v>
       </c>
-      <c r="C10" s="29" t="str">
+      <c r="E10" s="28" t="str">
         <f t="shared" si="1"/>
         <v>k</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>129</v>
-      </c>
-      <c r="F10" t="s">
-        <v>129</v>
+      <c r="F10">
+        <v>1</v>
       </c>
       <c r="G10" t="s">
         <v>129</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
+      <c r="H10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I10" t="s">
+        <v>129</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -4782,13 +4849,13 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>0</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -4830,13 +4897,13 @@
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10">
         <v>0</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10">
         <v>0</v>
@@ -4845,13 +4912,13 @@
         <v>0</v>
       </c>
       <c r="AK10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10">
         <v>0</v>
@@ -4869,13 +4936,13 @@
         <v>0</v>
       </c>
       <c r="AS10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT10">
         <v>0</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV10">
         <v>0</v>
@@ -4932,13 +4999,13 @@
         <v>0</v>
       </c>
       <c r="BN10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO10">
         <v>0</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ10">
         <v>0</v>
@@ -5034,13 +5101,13 @@
         <v>0</v>
       </c>
       <c r="CV10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW10">
         <v>0</v>
       </c>
       <c r="CX10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY10">
         <v>0</v>
@@ -5049,13 +5116,13 @@
         <v>0</v>
       </c>
       <c r="DA10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB10">
         <v>0</v>
       </c>
       <c r="DC10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD10">
         <v>0</v>
@@ -5070,13 +5137,13 @@
         <v>0</v>
       </c>
       <c r="DH10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI10">
         <v>0</v>
       </c>
       <c r="DJ10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK10">
         <v>0</v>
@@ -5112,59 +5179,65 @@
         <v>0</v>
       </c>
       <c r="DV10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW10">
         <v>0</v>
       </c>
       <c r="DX10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:129" x14ac:dyDescent="0.2">
-      <c r="A11" s="30" t="s">
+      <c r="DZ10">
+        <v>0</v>
+      </c>
+      <c r="EA10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:131" x14ac:dyDescent="0.2">
+      <c r="A11" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="B11" s="29" t="str">
+      <c r="B11" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="28">
+        <v>2025</v>
+      </c>
+      <c r="D11" s="28" t="str">
         <f t="shared" si="0"/>
         <v>bird_rock_2025-09-11_t1</v>
       </c>
-      <c r="C11" s="29" t="str">
+      <c r="E11" s="28" t="str">
         <f t="shared" si="1"/>
         <v>b</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>129</v>
-      </c>
-      <c r="F11" t="s">
-        <v>129</v>
+      <c r="F11">
+        <v>1</v>
       </c>
       <c r="G11" t="s">
         <v>129</v>
       </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
+      <c r="H11" t="s">
+        <v>129</v>
+      </c>
+      <c r="I11" t="s">
+        <v>129</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -5173,10 +5246,10 @@
         <v>1</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -5185,37 +5258,37 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11">
         <v>1</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC11">
         <v>0</v>
       </c>
       <c r="AD11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE11">
         <v>0</v>
@@ -5227,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11">
         <v>0</v>
@@ -5236,16 +5309,16 @@
         <v>0</v>
       </c>
       <c r="AK11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -5257,40 +5330,40 @@
         <v>0</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT11">
         <v>0</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV11">
         <v>0</v>
       </c>
       <c r="AW11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX11">
         <v>0</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ11">
         <v>0</v>
       </c>
       <c r="BA11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB11">
         <v>0</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD11">
         <v>0</v>
@@ -5323,22 +5396,22 @@
         <v>0</v>
       </c>
       <c r="BN11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO11">
         <v>0</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR11">
         <v>0</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT11">
         <v>0</v>
@@ -5356,28 +5429,28 @@
         <v>0</v>
       </c>
       <c r="BY11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC11">
         <v>0</v>
       </c>
       <c r="CD11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE11">
         <v>0</v>
       </c>
       <c r="CF11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG11">
         <v>0</v>
@@ -5386,13 +5459,13 @@
         <v>0</v>
       </c>
       <c r="CI11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ11">
         <v>0</v>
       </c>
       <c r="CK11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL11">
         <v>0</v>
@@ -5413,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="CR11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CS11">
         <v>0</v>
@@ -5425,19 +5498,19 @@
         <v>0</v>
       </c>
       <c r="CV11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW11">
         <v>0</v>
       </c>
       <c r="CX11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY11">
         <v>0</v>
       </c>
       <c r="CZ11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DA11">
         <v>0</v>
@@ -5461,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="DH11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI11">
         <v>0</v>
       </c>
       <c r="DJ11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK11">
         <v>0</v>
@@ -5476,25 +5549,25 @@
         <v>0</v>
       </c>
       <c r="DM11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR11">
         <v>0</v>
       </c>
       <c r="DS11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT11">
         <v>0</v>
@@ -5503,47 +5576,53 @@
         <v>0</v>
       </c>
       <c r="DV11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW11">
         <v>0</v>
       </c>
       <c r="DX11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:129" x14ac:dyDescent="0.2">
-      <c r="A12" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="DZ11">
+        <v>0</v>
+      </c>
+      <c r="EA11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:131" x14ac:dyDescent="0.2">
+      <c r="A12" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="B12" s="29" t="str">
+      <c r="B12" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="28">
+        <v>2025</v>
+      </c>
+      <c r="D12" s="28" t="str">
         <f t="shared" si="0"/>
         <v>hms110_2025-09-11_t1</v>
       </c>
-      <c r="C12" s="29" t="str">
+      <c r="E12" s="28" t="str">
         <f t="shared" si="1"/>
         <v>k</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>129</v>
-      </c>
-      <c r="F12" t="s">
-        <v>129</v>
+      <c r="F12">
+        <v>1</v>
       </c>
       <c r="G12" t="s">
         <v>129</v>
       </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
+      <c r="H12" t="s">
+        <v>129</v>
+      </c>
+      <c r="I12" t="s">
+        <v>129</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -5579,13 +5658,13 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12">
         <v>0</v>
@@ -5636,22 +5715,22 @@
         <v>0</v>
       </c>
       <c r="AN12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR12">
         <v>0</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT12">
         <v>0</v>
@@ -5714,13 +5793,13 @@
         <v>0</v>
       </c>
       <c r="BN12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO12">
         <v>0</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ12">
         <v>0</v>
@@ -5846,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="DF12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG12">
         <v>0</v>
@@ -5858,7 +5937,7 @@
         <v>0</v>
       </c>
       <c r="DJ12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK12">
         <v>0</v>
@@ -5867,13 +5946,13 @@
         <v>0</v>
       </c>
       <c r="DM12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN12">
         <v>0</v>
       </c>
       <c r="DO12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP12">
         <v>0</v>
@@ -5905,45 +5984,51 @@
       <c r="DY12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:129" x14ac:dyDescent="0.2">
-      <c r="A13" s="30" t="s">
+      <c r="DZ12">
+        <v>0</v>
+      </c>
+      <c r="EA12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:131" x14ac:dyDescent="0.2">
+      <c r="A13" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="29" t="str">
+      <c r="B13" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="C13" s="28">
+        <v>2025</v>
+      </c>
+      <c r="D13" s="28" t="str">
         <f t="shared" si="0"/>
         <v>hms110_2025-09-11_t1</v>
       </c>
-      <c r="C13" s="29" t="str">
+      <c r="E13" s="28" t="str">
         <f t="shared" si="1"/>
         <v>b</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>129</v>
-      </c>
-      <c r="F13" t="s">
-        <v>129</v>
+      <c r="F13">
+        <v>1</v>
       </c>
       <c r="G13" t="s">
         <v>129</v>
       </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
+      <c r="H13" t="s">
+        <v>129</v>
+      </c>
+      <c r="I13" t="s">
+        <v>129</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -5952,25 +6037,25 @@
         <v>0</v>
       </c>
       <c r="O13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13">
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -5988,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13">
         <v>0</v>
@@ -5997,22 +6082,22 @@
         <v>0</v>
       </c>
       <c r="AD13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AI13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
         <v>0</v>
@@ -6024,7 +6109,7 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN13">
         <v>0</v>
@@ -6036,16 +6121,16 @@
         <v>0</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU13">
         <v>0</v>
@@ -6054,13 +6139,13 @@
         <v>0</v>
       </c>
       <c r="AW13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX13">
         <v>0</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ13">
         <v>0</v>
@@ -6093,25 +6178,25 @@
         <v>0</v>
       </c>
       <c r="BJ13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK13">
         <v>0</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM13">
         <v>0</v>
       </c>
       <c r="BN13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO13">
         <v>0</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ13">
         <v>0</v>
@@ -6138,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="BY13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ13">
         <v>0</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB13">
         <v>0</v>
@@ -6171,22 +6256,22 @@
         <v>0</v>
       </c>
       <c r="CJ13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK13">
         <v>0</v>
       </c>
       <c r="CL13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP13">
         <v>1</v>
@@ -6195,19 +6280,19 @@
         <v>0</v>
       </c>
       <c r="CR13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CS13">
         <v>0</v>
       </c>
       <c r="CT13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU13">
         <v>0</v>
       </c>
       <c r="CV13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW13">
         <v>0</v>
@@ -6222,13 +6307,13 @@
         <v>0</v>
       </c>
       <c r="DA13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB13">
         <v>0</v>
       </c>
       <c r="DC13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD13">
         <v>0</v>
@@ -6243,13 +6328,13 @@
         <v>0</v>
       </c>
       <c r="DH13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI13">
         <v>0</v>
       </c>
       <c r="DJ13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK13">
         <v>0</v>
@@ -6258,28 +6343,28 @@
         <v>0</v>
       </c>
       <c r="DM13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU13">
         <v>0</v>
@@ -6294,6 +6379,12 @@
         <v>0</v>
       </c>
       <c r="DY13">
+        <v>0</v>
+      </c>
+      <c r="DZ13">
+        <v>0</v>
+      </c>
+      <c r="EA13">
         <v>0</v>
       </c>
     </row>
@@ -14502,47 +14593,47 @@
     <col min="14" max="14" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="L1" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="M1" s="30" t="s">
+      <c r="M1" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="N1" s="29" t="s">
         <v>126</v>
       </c>
     </row>
